--- a/payment_forms/016_food_truck_order_form--payment_forms.xlsx
+++ b/payment_forms/016_food_truck_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -792,8 +792,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -821,12 +821,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'credit_card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'paypal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new',_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New', 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'placed',_'label':_'placed'}</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Placed', 'label': 'Placed'}</t>
+          <t>Placed</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'shipped',_'label':_'shipped'}</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Shipped', 'label': 'Shipped'}</t>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'delivered',_'label':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Delivered', 'label': 'Delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'cancelled',_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Cancelled', 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
